--- a/FOA SETS/Nexoes-Set.xlsx
+++ b/FOA SETS/Nexoes-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,36 +595,35 @@
           <t>Nexoes</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Upholstery Set</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JAMBI Sofa  and  Loveseat</t>
+          <t>JAMBI Sofa and Loveseat</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-JAMBI Sofa  and  Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a nexoes upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Brown tones, the Breathable Leather, Solid Wood, Others build keeps the look polished and practical.
-Product Dimensions: 87.5" W x 41.5"D x 41" H
+JAMBI Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a nexoes upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Brown tones, the Breathable Leather, Solid Wood, build keeps the look polished and practical.
+Product Dimensions: 87.5"W X 41.5"D X 41"H
 Features
 - Pillow Top Arms
 - Console with Metal Cup Holders on Loveseat
-- Drop-down Table on Sofa with Metal Cup Holders
-Included items and dimensions:
+- Drop-down Table on Sofa with Metal Cup Holders Included items and dimensions:
 - Sofa: color: Brown; dimensions: 87.4" W x 41.3"D x 41.1" H; feature: Transitional
 - Loveseat: color: Brown; dimensions: 77" W x 41.3"D x 41.1" H; feature: Transitional
-Materials: Breathable Leather, Solid Wood, Others
+Materials: Breathable Leather, Solid Wood.
 Color: Brown
 Weight: 207 lbs</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JAMBI Sofa  and  Loveseat in Brown | GOODDEGG</t>
+          <t>JAMBI Sofa and Loveseat in Brown | GOODDEGG</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/FOA SETS/Nexoes-Set.xlsx
+++ b/FOA SETS/Nexoes-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,183 +429,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>seo title(70char)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>seo title(70char)</t>
+          <t>seo description(160char)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>seo description(160char)</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Short Description - Red Text</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Short Description - Red Text</t>
+          <t>Item Type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Parts for Group Items</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Parts for Group Items</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>East(cost)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>East(cost)</t>
+          <t>EAST COST (Updated)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>EAST COST (Updated)</t>
+          <t>MSRP</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>MSRP</t>
+          <t>Weight (LB)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Weight (LB)</t>
+          <t>Product Dimension (Inch)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Product Dimension (Inch)</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Shipping Length (IN)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Shipping Length (IN)</t>
+          <t>Shipping Width (IN)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Shipping Width (IN)</t>
+          <t>Shipping Height (IN)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Shipping Height (IN)</t>
+          <t>Volume (CUFT)</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Volume (CUFT)</t>
+          <t>Fixed tags</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Variable tags</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Brown</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NX6011BR-2PC</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NX6011BR-2PC</t>
+          <t>Nexoes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nexoes</t>
+          <t>Upholstery Set</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Upholstery Set</t>
+          <t>JAMBI Sofa and Loveseat</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>JAMBI Sofa and Loveseat</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 JAMBI Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a nexoes upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Brown tones, the Breathable Leather, Solid Wood, build keeps the look polished and practical.
@@ -621,80 +626,90 @@
 Weight: 207 lbs</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>JAMBI Sofa and Loveseat in Brown | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JAMBI Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>The JAMBI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>The JAMBI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMBI</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>JAMBI</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>Sofa + Loveseat</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>NX6011BR-SF, NX6011BR-LV</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>NX6011BR-SF, NX6011BR-LV</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>NX6011BR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="P2" t="n">
         <v>1059</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="Q2" s="1" t="n">
         <v>1059</v>
       </c>
+      <c r="R2" t="n">
+        <v>2217</v>
+      </c>
       <c r="S2" t="n">
-        <v>2217</v>
-      </c>
-      <c r="T2" t="n">
         <v>207</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>87.5"W X 41.5"D X 41"H</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>87.5"W X 41.5"D X 41"H</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Breathable Leather, Solid Wood, Others</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Breathable Leather, Solid Wood, Others</t>
+          <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Console with Metal Cup Holders on Loveseat,Drop-down Table on Sofa with Metal Cup Holders</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Console with Metal Cup Holders on Loveseat,Drop-down Table on Sofa with Metal Cup Holders</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC2" t="n">
+      <c r="AB2" t="n">
         <v>89.3</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Nexoes, Upholstery Set, JAMBI</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/FOA SETS/Nexoes-Set.xlsx
+++ b/FOA SETS/Nexoes-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,18 +612,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JAMBI Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a nexoes upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Brown tones, the Breathable Leather, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 87.5"W X 41.5"D X 41"H
-Features
-- Pillow Top Arms
-- Console with Metal Cup Holders on Loveseat
-- Drop-down Table on Sofa with Metal Cup Holders Included items and dimensions:
-- Sofa: color: Brown; dimensions: 87.4" W x 41.3"D x 41.1" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 77" W x 41.3"D x 41.1" H; feature: Transitional
-Materials: Breathable Leather, Solid Wood.
-Color: Brown
-Weight: 207 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JAMBI Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a nexoes upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Brown tones, the Breathable Leather, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 87.5"W X 41.5"D X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Console with Metal Cup Holders on Loveseat&lt;br&gt;
+- Drop-down Table on Sofa with Metal Cup Holders Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 87.4" W x 41.3"D x 41.1" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 77" W x 41.3"D x 41.1" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leather, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 207 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/FOA SETS/Nexoes-Set.xlsx
+++ b/FOA SETS/Nexoes-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,6 +581,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -708,7 +723,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Nexoes, Upholstery Set, JAMBI</t>
+          <t>Nexoes, Upholstery Set, JAMBI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>

--- a/FOA SETS/Nexoes-Set.xlsx
+++ b/FOA SETS/Nexoes-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">

--- a/FOA SETS/Nexoes-Set.xlsx
+++ b/FOA SETS/Nexoes-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,12 +643,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JAMBI Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>JAMBI Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The JAMBI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMBI Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/FOA SETS/Nexoes-Set.xlsx
+++ b/FOA SETS/Nexoes-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,171 +429,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seo title(70char)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>seo description(160char)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Short Description - Red Text</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Item Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Parts for Group Items</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Images</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Image src</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>combine image src</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>East(cost)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>EAST COST (Updated)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MSRP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Weight (LB)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Dimension (Inch)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Shipping Length (IN)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Shipping Width (IN)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Shipping Height (IN)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Volume (CUFT)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Fixed tags</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Variable tags</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
@@ -602,30 +617,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>jambi-sofa-and-loveseat</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Brown</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>NX6011BR-2PC</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Nexoes</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Upholstery Set</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>JAMBI Sofa and Loveseat</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 JAMBI Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a nexoes upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Brown tones, the Breathable Leather, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
@@ -641,102 +661,108 @@
 Weight: 207 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>JAMBI Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>JAMBI Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>JAMBI</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Sofa + Loveseat</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>NX6011BR-SF, NX6011BR-LV</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>NX6011BR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>NX6011BR-1-Z.jpg</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>1059</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="T2" s="1" t="n">
         <v>1059</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>2217</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>207</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>87.5"W X 41.5"D X 41"H</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Breathable Leather, Solid Wood, Others</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Console with Metal Cup Holders on Loveseat,Drop-down Table on Sofa with Metal Cup Holders</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>89.3</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Nexoes, Upholstery Set, JAMBI, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
